--- a/BieuMau_SoLieu_TuyenGiao.xlsx
+++ b/BieuMau_SoLieu_TuyenGiao.xlsx
@@ -111,7 +111,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -133,11 +133,55 @@
         <color rgb="00BFC7D2"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFC7D2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFC7D2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFC7D2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFC7D2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFC7D2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFC7D2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFC7D2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFC7D2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -178,6 +222,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -631,10 +677,10 @@
           <t>Văn bản tham mưu</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="16" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
@@ -768,10 +814,10 @@
           <t>Lý luận chính trị</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="16" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
@@ -1031,10 +1077,10 @@
           <t>Học tập, quán triệt nghị quyết</t>
         </is>
       </c>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="16" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="9" t="n">
@@ -1252,10 +1298,10 @@
           <t>Tuyên truyền, báo chí - xuất bản</t>
         </is>
       </c>
-      <c r="B42" s="8" t="n"/>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="8" t="n"/>
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="15" t="n"/>
+      <c r="E42" s="16" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="9" t="n">
@@ -1473,10 +1519,10 @@
           <t>Dư luận xã hội, bảo vệ nền tảng tư tưởng</t>
         </is>
       </c>
-      <c r="B53" s="8" t="n"/>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
-      <c r="E53" s="8" t="n"/>
+      <c r="B53" s="15" t="n"/>
+      <c r="C53" s="15" t="n"/>
+      <c r="D53" s="15" t="n"/>
+      <c r="E53" s="16" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="9" t="n">
@@ -1652,10 +1698,10 @@
           <t>Khoa giáo (Bình dân học vụ số)</t>
         </is>
       </c>
-      <c r="B62" s="8" t="n"/>
-      <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
-      <c r="E62" s="8" t="n"/>
+      <c r="B62" s="15" t="n"/>
+      <c r="C62" s="15" t="n"/>
+      <c r="D62" s="15" t="n"/>
+      <c r="E62" s="16" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="9" t="n">
@@ -2007,8 +2053,8 @@
     <mergeCell ref="A18:E18"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="D4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Loại kỳ" error="Chọn một trong: Tháng, Quý, 6 tháng, 9 tháng, Năm" type="list">
-      <formula1>"Tháng,Quý,6 tháng,9 tháng,Năm"</formula1>
+    <dataValidation sqref="D4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Loại kỳ" error="Chọn một trong: Tháng, Quý, 6 tháng, 9 tháng, 10 tháng, 11 tháng, Năm" type="list">
+      <formula1>"Tháng,Quý,6 tháng,9 tháng,10 tháng,11 tháng,Năm"</formula1>
     </dataValidation>
     <dataValidation sqref="D5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Nhập số tháng 1-12 hoặc số quý 1-4" type="whole" operator="between">
       <formula1>1</formula1>
@@ -2049,7 +2095,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>1. Chọn Loại kỳ báo cáo ở ô D4: Tháng, Quý, 6 tháng, 9 tháng hoặc Năm.</t>
+          <t>1. Chọn Loại kỳ báo cáo ở ô D4: Tháng, Quý, 6 tháng, 9 tháng, 10 tháng, 11 tháng hoặc Năm (các kỳ nhiều tháng là lũy kế từ đầu năm).</t>
         </is>
       </c>
     </row>
